--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Notre équipe vous propose un restaurant 75006 d'une capacité de 24 couverts et une cuisine de plain pieds avec extraction de 400 tenu depuis 13 ans par un cuisinier japonais réalisant une cuisine bistrotière. Affaire clé en mains le matériel est récent et bien entretenu. Terrasse éphémère de 14 places. Le CA annuel moyen sur les trois dernières années est de 255K euros .Loyer de 2252 euros ttc cc /mois. Prix de cession 200K euros net vendeur. Fermeture dimanche et lundi midi. Disponibilité : Immédiate Bus Maine - Vaugirard (28, 82, 89, 92), Duroc (86), Vaneau - Saint-Romain (70) Métro Duroc (1</t>
+          <t>Notre équipe vous propose un restaurant 75006 d'une capacité de 24 couverts et une cuisine de plain pieds avec extraction de 400 tenu depuis 13 ans par un cuisinier japonais réalisant une cuisine bistrotière. Affaire clé en mains le matériel est récent et bien entretenu. Terrasse éphémère de 14 places. Le CA annuel moyen sur les trois dernières années est de 255K euros .Loyer de 2252 euros ttc cc /mois. Prix de cession 200K euros net vendeur. Fermeture dimanche et lundi midi. Disponibilité : Immédiate Bus Maine - Vaugirard (28, 82, 89, 92), Duroc (86), Vaneau - Saint-Romain (70) Métro Duroc (10, 13), Falguière (12), Montparnasse Bienvenue (4, 6) SNCF Paris-Montparnasse (France) Transilien Gare Montparnasse (TER), Paris Montparnasse (TER) Transilien Gare Montparnasse (N)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +810 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +796 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
+++ b/docs/dossiers/dossier-paris-6e-7972f6d3.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
